--- a/outputs/monitor_xlsx/20260226.xlsx
+++ b/outputs/monitor_xlsx/20260226.xlsx
@@ -999,7 +999,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W26"/>
+  <dimension ref="A1:W27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -2447,7 +2447,7 @@
         <v>-106273</v>
       </c>
       <c r="N25" t="n">
-        <v>28.2</v>
+        <v>23.26</v>
       </c>
       <c r="O25" t="inlineStr">
         <is>
@@ -2505,6 +2505,59 @@
       <c r="O26" t="inlineStr">
         <is>
           <t>偏多</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>6515</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>穎崴</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>5115</v>
+      </c>
+      <c r="D27" s="6" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="E27" t="n">
+        <v>1016</v>
+      </c>
+      <c r="F27" s="6" t="n">
+        <v>-90</v>
+      </c>
+      <c r="G27" t="n">
+        <v>-71</v>
+      </c>
+      <c r="H27" t="n">
+        <v>74</v>
+      </c>
+      <c r="I27" t="n">
+        <v>-39</v>
+      </c>
+      <c r="J27" t="n">
+        <v>11</v>
+      </c>
+      <c r="K27" t="n">
+        <v>279</v>
+      </c>
+      <c r="L27" t="n">
+        <v>1696</v>
+      </c>
+      <c r="M27" t="n">
+        <v>-8884</v>
+      </c>
+      <c r="N27" t="n">
+        <v>6.74</v>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>主力積極賣出</t>
         </is>
       </c>
     </row>

--- a/outputs/monitor_xlsx/20260226.xlsx
+++ b/outputs/monitor_xlsx/20260226.xlsx
@@ -461,7 +461,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H14"/>
+  <dimension ref="A1:H18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -526,215 +526,236 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>總經</t>
+          <t>大盤</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>美債10年殖利率</t>
+          <t>加權指數 (TWII)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>4.02%</t>
+          <t>35414.49</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.69%</t>
-        </is>
-      </c>
+          <t>+0.00%</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>總經</t>
+          <t>大盤</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>黃金指數 (GC=F)</t>
+          <t>櫃買指數 (OTC)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>5176.5$</t>
+          <t>316.73</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>-0.57%</t>
-        </is>
-      </c>
+          <t>+1.11%</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>貨幣</t>
+          <t>大盤</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>美元/台幣匯率</t>
+          <t>台指近月期貨</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>31.27</t>
+          <t>35604.0</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.34%</t>
-        </is>
-      </c>
+          <t>+0.32%</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>現貨</t>
+          <t>總經</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>費半指數 (SOX)</t>
+          <t>美債10年殖利率</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>8197.26</t>
+          <t>4.02%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>-3.19%</t>
-        </is>
-      </c>
+          <t>-0.69%</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>情緒</t>
+          <t>總經</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>恐慌指數 (VIX)</t>
+          <t>黃金指數 (GC=F)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>18.63</t>
+          <t>5176.5$</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>+3.90%</t>
-        </is>
-      </c>
+          <t>-0.57%</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>籌碼</t>
+          <t>貨幣</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>外資現貨</t>
+          <t>美元/台幣匯率</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>308.06億</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>1540.3億</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>70.67億</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>1413.46億</t>
-        </is>
-      </c>
+          <t>31.27</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>-0.34%</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>籌碼</t>
+          <t>現貨</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>投信現貨</t>
+          <t>費半指數 (SOX)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>24.63億</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>123.17億</t>
-        </is>
-      </c>
+          <t>8197.26</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>-3.19%</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>籌碼</t>
+          <t>情緒</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>選擇權 P/C Ratio</t>
+          <t>恐慌指數 (VIX)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>153.95%</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>175.11%</t>
-        </is>
-      </c>
+          <t>18.63</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>+3.90%</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>籌碼</t>
+          <t>原物料</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>三大法人合計</t>
+          <t>WTI原油期貨</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
+          <t>65.21$</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>-0.32%</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -744,54 +765,175 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>外資期貨未平倉</t>
+          <t>外資現貨</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>7495口</t>
-        </is>
-      </c>
+          <t>-105.64億</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>None口</t>
+          <t>308.06億</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>1540.3億</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>None億</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>None億</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
+          <t>籌碼</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>投信現貨</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>-10.58億</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>24.63億</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>123.17億</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>籌碼</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>選擇權 P/C Ratio</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>141.14%</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>None%</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>籌碼</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>三大法人合計</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>-134.21億</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>籌碼</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>外資期貨未平倉</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>7495口</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>11853口</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>結算</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>融資融券變化</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C18" t="inlineStr">
         <is>
           <t>-70.69億</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr">
         <is>
           <t>-41.41億</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="F18" t="inlineStr">
         <is>
           <t>-207.07億</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>-14.97億</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>-299.35億</t>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>None億</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>None億</t>
         </is>
       </c>
     </row>
@@ -862,7 +1004,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>70.67億</t>
+          <t>None億</t>
         </is>
       </c>
     </row>
@@ -874,9 +1016,13 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>1413.46億</t>
-        </is>
-      </c>
+          <t>None億</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr"/>
+      <c r="B8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -941,7 +1087,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>-14.97億</t>
+          <t>None億</t>
         </is>
       </c>
     </row>
@@ -953,7 +1099,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>-299.35億</t>
+          <t>None億</t>
         </is>
       </c>
     </row>
@@ -972,7 +1118,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>175.11%</t>
+          <t>None%</t>
         </is>
       </c>
     </row>
@@ -984,7 +1130,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>None口</t>
+          <t>11853口</t>
         </is>
       </c>
     </row>
@@ -999,7 +1145,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W27"/>
+  <dimension ref="A1:V16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1018,13 +1164,12 @@
     <col width="12" customWidth="1" min="14" max="14"/>
     <col width="12" customWidth="1" min="15" max="15"/>
     <col width="12" customWidth="1" min="16" max="16"/>
-    <col width="12" customWidth="1" min="17" max="17"/>
+    <col width="14" customWidth="1" min="17" max="17"/>
     <col width="14" customWidth="1" min="18" max="18"/>
-    <col width="14" customWidth="1" min="19" max="19"/>
-    <col width="12" customWidth="1" min="20" max="20"/>
-    <col width="10" customWidth="1" min="21" max="21"/>
-    <col width="12" customWidth="1" min="22" max="22"/>
-    <col width="10" customWidth="1" min="23" max="23"/>
+    <col width="12" customWidth="1" min="19" max="19"/>
+    <col width="10" customWidth="1" min="20" max="20"/>
+    <col width="12" customWidth="1" min="21" max="21"/>
+    <col width="10" customWidth="1" min="22" max="22"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1034,7 +1179,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
@@ -1113,40 +1257,35 @@
       </c>
       <c r="P3" s="5" t="inlineStr">
         <is>
-          <t>籌碼評價</t>
+          <t>買賣券商差</t>
         </is>
       </c>
       <c r="Q3" s="5" t="inlineStr">
         <is>
-          <t>買賣券商差</t>
+          <t>籌碼集中度5D(%)</t>
         </is>
       </c>
       <c r="R3" s="5" t="inlineStr">
         <is>
-          <t>籌碼集中度5D(%)</t>
+          <t>借券賣出餘額</t>
         </is>
       </c>
       <c r="S3" s="5" t="inlineStr">
         <is>
-          <t>借券賣出餘額</t>
+          <t>短回補天數</t>
         </is>
       </c>
       <c r="T3" s="5" t="inlineStr">
         <is>
-          <t>短回補天數</t>
+          <t>VWAP20D</t>
         </is>
       </c>
       <c r="U3" s="5" t="inlineStr">
         <is>
-          <t>VWAP20D</t>
+          <t>VWAP乖離(%)</t>
         </is>
       </c>
       <c r="V3" s="5" t="inlineStr">
-        <is>
-          <t>VWAP乖離(%)</t>
-        </is>
-      </c>
-      <c r="W3" s="5" t="inlineStr">
         <is>
           <t>資料來源</t>
         </is>
@@ -1181,10 +1320,10 @@
         <v>-19326</v>
       </c>
       <c r="H4" t="n">
-        <v>-27120</v>
+        <v>-134274</v>
       </c>
       <c r="J4" t="n">
-        <v>25026</v>
+        <v>30200</v>
       </c>
       <c r="K4" t="n">
         <v>65045</v>
@@ -1193,20 +1332,12 @@
         <v>8471</v>
       </c>
       <c r="M4" t="n">
-        <v>37320</v>
+        <v>30912</v>
       </c>
       <c r="N4" t="n">
         <v>-4112378</v>
       </c>
-      <c r="O4" t="n">
-        <v>7.93</v>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>偏空</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1215,41 +1346,53 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>00708L</t>
+          <t>1519</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>S&amp;P黃金正2</t>
-        </is>
+          <t>華城</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>1070</v>
+      </c>
+      <c r="E5" s="6" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="F5" t="n">
+        <v>10806</v>
       </c>
       <c r="G5" s="7" t="n">
-        <v>240</v>
+        <v>1982</v>
       </c>
       <c r="H5" t="n">
-        <v>-129</v>
+        <v>1888</v>
+      </c>
+      <c r="I5" t="n">
+        <v>-82</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>-815</v>
       </c>
       <c r="K5" t="n">
-        <v>1182</v>
+        <v>376</v>
       </c>
       <c r="L5" t="n">
-        <v>9683</v>
+        <v>2840</v>
       </c>
       <c r="M5" t="n">
-        <v>49267</v>
+        <v>11896</v>
       </c>
       <c r="N5" t="n">
-        <v>-28035</v>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>主力積極賣出</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
+        <v>-78740</v>
+      </c>
+      <c r="V5" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1258,12 +1401,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>1519</t>
+          <t>2308</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>華城</t>
+          <t>台達電</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1272,47 +1415,39 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>1070</v>
-      </c>
-      <c r="E6" s="6" t="n">
-        <v>1.9</v>
+        <v>1430</v>
+      </c>
+      <c r="E6" s="7" t="n">
+        <v>-0.35</v>
       </c>
       <c r="F6" t="n">
-        <v>10806</v>
-      </c>
-      <c r="G6" s="7" t="n">
-        <v>1982</v>
+        <v>17965</v>
+      </c>
+      <c r="G6" s="6" t="n">
+        <v>-2362</v>
       </c>
       <c r="H6" t="n">
-        <v>1730</v>
+        <v>5813</v>
       </c>
       <c r="I6" t="n">
-        <v>-82</v>
+        <v>987</v>
       </c>
       <c r="J6" t="n">
-        <v>-1154</v>
+        <v>2183</v>
       </c>
       <c r="K6" t="n">
-        <v>376</v>
+        <v>391</v>
       </c>
       <c r="L6" t="n">
-        <v>2840</v>
+        <v>6549</v>
       </c>
       <c r="M6" t="n">
-        <v>14357</v>
+        <v>26276</v>
       </c>
       <c r="N6" t="n">
-        <v>-78740</v>
-      </c>
-      <c r="O6" t="n">
-        <v>12.54</v>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>中性</t>
-        </is>
-      </c>
-      <c r="W6" t="inlineStr">
+        <v>-648840</v>
+      </c>
+      <c r="V6" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1321,12 +1456,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2308</t>
+          <t>2330</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>台達電</t>
+          <t>台積電</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1335,47 +1470,39 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>1430</v>
+        <v>1995</v>
       </c>
       <c r="E7" s="7" t="n">
-        <v>-0.35</v>
+        <v>-0.99</v>
       </c>
       <c r="F7" t="n">
-        <v>17965</v>
+        <v>74411</v>
       </c>
       <c r="G7" s="6" t="n">
-        <v>-2362</v>
+        <v>-18137</v>
       </c>
       <c r="H7" t="n">
-        <v>1292</v>
+        <v>-19805</v>
       </c>
       <c r="I7" t="n">
-        <v>987</v>
+        <v>1202</v>
       </c>
       <c r="J7" t="n">
-        <v>1974</v>
+        <v>7692</v>
       </c>
       <c r="K7" t="n">
-        <v>391</v>
+        <v>520</v>
       </c>
       <c r="L7" t="n">
-        <v>6549</v>
+        <v>22312</v>
       </c>
       <c r="M7" t="n">
-        <v>31255</v>
+        <v>85837</v>
       </c>
       <c r="N7" t="n">
-        <v>-648840</v>
-      </c>
-      <c r="O7" t="n">
-        <v>17.41</v>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>偏多</t>
-        </is>
-      </c>
-      <c r="W7" t="inlineStr">
+        <v>-6482906</v>
+      </c>
+      <c r="V7" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1384,12 +1511,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2330</t>
+          <t>2345</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>台積電</t>
+          <t>智邦</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1398,47 +1525,39 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>1995</v>
+        <v>1400</v>
       </c>
       <c r="E8" s="7" t="n">
-        <v>-0.99</v>
+        <v>-3.45</v>
       </c>
       <c r="F8" t="n">
-        <v>74411</v>
+        <v>5719</v>
       </c>
       <c r="G8" s="6" t="n">
-        <v>-18137</v>
+        <v>-565</v>
       </c>
       <c r="H8" t="n">
-        <v>-13521</v>
+        <v>724</v>
       </c>
       <c r="I8" t="n">
-        <v>1202</v>
+        <v>-184</v>
       </c>
       <c r="J8" t="n">
-        <v>4933</v>
+        <v>474</v>
       </c>
       <c r="K8" t="n">
-        <v>520</v>
+        <v>154</v>
       </c>
       <c r="L8" t="n">
-        <v>22312</v>
+        <v>1931</v>
       </c>
       <c r="M8" t="n">
-        <v>110248</v>
+        <v>7424</v>
       </c>
       <c r="N8" t="n">
-        <v>-6482906</v>
-      </c>
-      <c r="O8" t="n">
-        <v>7.37</v>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>偏空</t>
-        </is>
-      </c>
-      <c r="W8" t="inlineStr">
+        <v>-140163</v>
+      </c>
+      <c r="V8" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1447,12 +1566,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2344</t>
+          <t>2360</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>華邦電</t>
+          <t>致茂</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1461,47 +1580,39 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>122.5</v>
+        <v>1380</v>
       </c>
       <c r="E9" s="6" t="n">
-        <v>3.81</v>
+        <v>9.960000000000001</v>
       </c>
       <c r="F9" t="n">
-        <v>180884</v>
-      </c>
-      <c r="G9" s="7" t="n">
-        <v>27413</v>
+        <v>2642</v>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>-1460</v>
       </c>
       <c r="H9" t="n">
-        <v>-1407</v>
+        <v>-1394</v>
       </c>
       <c r="I9" t="n">
-        <v>3344</v>
+        <v>-782</v>
       </c>
       <c r="J9" t="n">
-        <v>6074</v>
+        <v>878</v>
       </c>
       <c r="K9" t="n">
-        <v>1734</v>
+        <v>4</v>
       </c>
       <c r="L9" t="n">
-        <v>137420</v>
+        <v>1765</v>
       </c>
       <c r="M9" t="n">
-        <v>690444</v>
+        <v>4622</v>
       </c>
       <c r="N9" t="n">
-        <v>-1111267</v>
-      </c>
-      <c r="O9" t="n">
-        <v>15.72</v>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>偏空</t>
-        </is>
-      </c>
-      <c r="W9" t="inlineStr">
+        <v>-106273</v>
+      </c>
+      <c r="V9" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1536,13 +1647,13 @@
         <v>-45</v>
       </c>
       <c r="H10" t="n">
-        <v>-2134</v>
+        <v>-1610</v>
       </c>
       <c r="I10" t="n">
         <v>-46</v>
       </c>
       <c r="J10" t="n">
-        <v>1919</v>
+        <v>1487</v>
       </c>
       <c r="K10" t="n">
         <v>83</v>
@@ -1551,20 +1662,12 @@
         <v>2177</v>
       </c>
       <c r="M10" t="n">
-        <v>10853</v>
+        <v>8753</v>
       </c>
       <c r="N10" t="n">
         <v>-89468</v>
       </c>
-      <c r="O10" t="n">
-        <v>16.41</v>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>偏空</t>
-        </is>
-      </c>
-      <c r="W10" t="inlineStr">
+      <c r="V10" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1573,12 +1676,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>3661</t>
+          <t>6442</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>世芯-KY</t>
+          <t>光聖</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1587,47 +1690,39 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>3490</v>
+        <v>2145</v>
       </c>
       <c r="E11" s="6" t="n">
-        <v>0.29</v>
+        <v>3.12</v>
       </c>
       <c r="F11" t="n">
-        <v>1524</v>
+        <v>1361</v>
       </c>
       <c r="G11" s="7" t="n">
-        <v>35</v>
+        <v>66</v>
       </c>
       <c r="H11" t="n">
-        <v>186</v>
+        <v>134</v>
       </c>
       <c r="I11" t="n">
-        <v>24</v>
+        <v>-10</v>
       </c>
       <c r="J11" t="n">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="K11" t="n">
-        <v>41</v>
+        <v>28</v>
       </c>
       <c r="L11" t="n">
-        <v>5832</v>
+        <v>4245</v>
       </c>
       <c r="M11" t="n">
-        <v>29724</v>
+        <v>16753</v>
       </c>
       <c r="N11" t="n">
-        <v>-19715</v>
-      </c>
-      <c r="O11" t="n">
-        <v>6.34</v>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>偏多</t>
-        </is>
-      </c>
-      <c r="W11" t="inlineStr">
+        <v>-19134</v>
+      </c>
+      <c r="V11" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1636,12 +1731,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>4958</t>
+          <t>6515</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>臻鼎-KY</t>
+          <t>穎崴</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1650,47 +1745,39 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>209</v>
+        <v>5115</v>
       </c>
       <c r="E12" s="6" t="n">
-        <v>1.7</v>
+        <v>2.3</v>
       </c>
       <c r="F12" t="n">
-        <v>35951</v>
+        <v>1016</v>
       </c>
       <c r="G12" s="6" t="n">
-        <v>-1759</v>
+        <v>-90</v>
       </c>
       <c r="H12" t="n">
-        <v>-744</v>
+        <v>19</v>
       </c>
       <c r="I12" t="n">
-        <v>-88</v>
+        <v>74</v>
       </c>
       <c r="J12" t="n">
-        <v>1357</v>
+        <v>-113</v>
       </c>
       <c r="K12" t="n">
-        <v>639</v>
+        <v>11</v>
       </c>
       <c r="L12" t="n">
-        <v>23015</v>
+        <v>279</v>
       </c>
       <c r="M12" t="n">
-        <v>129009</v>
+        <v>1417</v>
       </c>
       <c r="N12" t="n">
-        <v>-267352</v>
-      </c>
-      <c r="O12" t="n">
-        <v>13.9</v>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>偏空</t>
-        </is>
-      </c>
-      <c r="W12" t="inlineStr">
+        <v>-8884</v>
+      </c>
+      <c r="V12" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1699,61 +1786,53 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>6442</t>
+          <t>3081</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>光聖</t>
+          <t>聯亞</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>上市</t>
+          <t>上櫃</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>2145</v>
+        <v>2315</v>
       </c>
       <c r="E13" s="6" t="n">
-        <v>3.12</v>
+        <v>9.98</v>
       </c>
       <c r="F13" t="n">
-        <v>1361</v>
-      </c>
-      <c r="G13" s="7" t="n">
-        <v>66</v>
+        <v>2730</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>-160</v>
       </c>
       <c r="H13" t="n">
-        <v>543</v>
+        <v>-306</v>
       </c>
       <c r="I13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="J13" t="n">
+        <v>-22</v>
+      </c>
+      <c r="K13" t="n">
         <v>-10</v>
       </c>
-      <c r="J13" t="n">
-        <v>7</v>
-      </c>
-      <c r="K13" t="n">
-        <v>28</v>
-      </c>
       <c r="L13" t="n">
-        <v>4245</v>
+        <v>10</v>
       </c>
       <c r="M13" t="n">
-        <v>21194</v>
+        <v>-233</v>
       </c>
       <c r="N13" t="n">
-        <v>-19134</v>
-      </c>
-      <c r="O13" t="n">
-        <v>12.72</v>
-      </c>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>偏多</t>
-        </is>
-      </c>
-      <c r="W13" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="V13" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1762,12 +1841,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>3081</t>
+          <t>4979</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>聯亞</t>
+          <t>華星光</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1776,47 +1855,39 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>1250</v>
-      </c>
-      <c r="E14" s="7" t="n">
-        <v>-1.19</v>
+        <v>449.5</v>
+      </c>
+      <c r="E14" s="6" t="n">
+        <v>4.78</v>
       </c>
       <c r="F14" t="n">
-        <v>1043</v>
+        <v>3871</v>
       </c>
       <c r="G14" s="6" t="n">
-        <v>-160</v>
+        <v>-2009</v>
       </c>
       <c r="H14" t="n">
-        <v>44</v>
+        <v>3764</v>
       </c>
       <c r="I14" t="n">
-        <v>0</v>
+        <v>312</v>
       </c>
       <c r="J14" t="n">
-        <v>151</v>
+        <v>2486</v>
       </c>
       <c r="K14" t="n">
-        <v>-10</v>
+        <v>28</v>
       </c>
       <c r="L14" t="n">
-        <v>10</v>
+        <v>515</v>
       </c>
       <c r="M14" t="n">
-        <v>-227</v>
+        <v>-2042</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
       </c>
-      <c r="O14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>主力積極買進</t>
-        </is>
-      </c>
-      <c r="W14" t="inlineStr">
+      <c r="V14" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1825,12 +1896,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>3260</t>
+          <t>6187</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>威剛</t>
+          <t>萬潤</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1839,47 +1910,36 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>285.5</v>
-      </c>
-      <c r="E15" s="7" t="n">
-        <v>-4.19</v>
+        <v>974</v>
+      </c>
+      <c r="E15" s="6" t="n">
+        <v>9.93</v>
       </c>
       <c r="F15" t="n">
-        <v>17804</v>
-      </c>
-      <c r="G15" s="6" t="n">
-        <v>-1050</v>
+        <v>1350</v>
+      </c>
+      <c r="G15" s="7" t="n">
+        <v>2339</v>
       </c>
       <c r="H15" t="n">
-        <v>-4121</v>
-      </c>
-      <c r="I15" t="n">
-        <v>-1501</v>
+        <v>10086</v>
       </c>
       <c r="J15" t="n">
-        <v>-80</v>
+        <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>-20</v>
+        <v>18</v>
       </c>
       <c r="L15" t="n">
-        <v>-133</v>
+        <v>464</v>
       </c>
       <c r="M15" t="n">
-        <v>-769</v>
+        <v>-686</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
       </c>
-      <c r="O15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>偏空</t>
-        </is>
-      </c>
-      <c r="W15" t="inlineStr">
+      <c r="V15" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1888,12 +1948,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>3265</t>
+          <t>6640</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>台新科</t>
+          <t>均華</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1902,662 +1962,41 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>150</v>
+        <v>1600</v>
       </c>
       <c r="E16" s="6" t="n">
-        <v>3.45</v>
+        <v>4.92</v>
       </c>
       <c r="F16" t="n">
-        <v>5305</v>
-      </c>
-      <c r="G16" s="6" t="n">
-        <v>-294</v>
+        <v>904</v>
+      </c>
+      <c r="G16" s="7" t="n">
+        <v>78</v>
       </c>
       <c r="H16" t="n">
-        <v>1309</v>
+        <v>7</v>
       </c>
       <c r="I16" t="n">
-        <v>0</v>
+        <v>-33</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>-85</v>
       </c>
       <c r="K16" t="n">
-        <v>274</v>
+        <v>-8</v>
       </c>
       <c r="L16" t="n">
-        <v>38</v>
+        <v>-2</v>
       </c>
       <c r="M16" t="n">
-        <v>-188</v>
+        <v>-8</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
       </c>
-      <c r="O16" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>主力積極買進</t>
-        </is>
-      </c>
-      <c r="W16" t="inlineStr">
+      <c r="V16" t="inlineStr">
         <is>
           <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>4979</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>華星光</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="D17" t="n">
-        <v>421.5</v>
-      </c>
-      <c r="E17" s="6" t="n">
-        <v>4.07</v>
-      </c>
-      <c r="F17" t="n">
-        <v>31393</v>
-      </c>
-      <c r="G17" s="6" t="n">
-        <v>-2009</v>
-      </c>
-      <c r="H17" t="n">
-        <v>1308</v>
-      </c>
-      <c r="I17" t="n">
-        <v>312</v>
-      </c>
-      <c r="J17" t="n">
-        <v>2540</v>
-      </c>
-      <c r="K17" t="n">
-        <v>28</v>
-      </c>
-      <c r="L17" t="n">
-        <v>515</v>
-      </c>
-      <c r="M17" t="n">
-        <v>-645</v>
-      </c>
-      <c r="N17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="inlineStr">
-        <is>
-          <t>主力積極買進</t>
-        </is>
-      </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>3189</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>景碩</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="D18" t="n">
-        <v>314.5</v>
-      </c>
-      <c r="E18" s="7" t="n">
-        <v>-3.38</v>
-      </c>
-      <c r="F18" t="n">
-        <v>51206</v>
-      </c>
-      <c r="G18" s="6" t="n">
-        <v>-6830</v>
-      </c>
-      <c r="H18" t="n">
-        <v>-4252</v>
-      </c>
-      <c r="I18" t="n">
-        <v>-270</v>
-      </c>
-      <c r="J18" t="n">
-        <v>1387</v>
-      </c>
-      <c r="K18" t="n">
-        <v>2525</v>
-      </c>
-      <c r="L18" t="n">
-        <v>19610</v>
-      </c>
-      <c r="M18" t="n">
-        <v>105281</v>
-      </c>
-      <c r="N18" t="n">
-        <v>-113413</v>
-      </c>
-      <c r="O18" t="n">
-        <v>20.18</v>
-      </c>
-      <c r="P18" t="inlineStr">
-        <is>
-          <t>偏空</t>
-        </is>
-      </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>6669</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>緯穎</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="D19" t="n">
-        <v>4000</v>
-      </c>
-      <c r="E19" s="7" t="n">
-        <v>-1.48</v>
-      </c>
-      <c r="F19" t="n">
-        <v>2814</v>
-      </c>
-      <c r="G19" s="6" t="n">
-        <v>-168</v>
-      </c>
-      <c r="H19" t="n">
-        <v>777</v>
-      </c>
-      <c r="I19" t="n">
-        <v>-88</v>
-      </c>
-      <c r="J19" t="n">
-        <v>-176</v>
-      </c>
-      <c r="K19" t="n">
-        <v>149</v>
-      </c>
-      <c r="L19" t="n">
-        <v>2196</v>
-      </c>
-      <c r="M19" t="n">
-        <v>11337</v>
-      </c>
-      <c r="N19" t="n">
-        <v>-46416</v>
-      </c>
-      <c r="O19" t="n">
-        <v>7.99</v>
-      </c>
-      <c r="P19" t="inlineStr">
-        <is>
-          <t>中性</t>
-        </is>
-      </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>3138</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>耀登</t>
-        </is>
-      </c>
-      <c r="C20" t="n">
-        <v>198</v>
-      </c>
-      <c r="D20" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="E20" t="n">
-        <v>7631</v>
-      </c>
-      <c r="F20" s="7" t="n">
-        <v>480</v>
-      </c>
-      <c r="G20" t="n">
-        <v>-729</v>
-      </c>
-      <c r="H20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I20" t="n">
-        <v>0</v>
-      </c>
-      <c r="J20" t="n">
-        <v>41</v>
-      </c>
-      <c r="K20" t="n">
-        <v>4811</v>
-      </c>
-      <c r="L20" t="n">
-        <v>22507</v>
-      </c>
-      <c r="M20" t="n">
-        <v>-11306</v>
-      </c>
-      <c r="N20" t="n">
-        <v>11.19</v>
-      </c>
-      <c r="O20" t="inlineStr">
-        <is>
-          <t>主力積極賣出</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>2404</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>漢唐</t>
-        </is>
-      </c>
-      <c r="C21" t="n">
-        <v>1130</v>
-      </c>
-      <c r="D21" s="6" t="n">
-        <v>9.18</v>
-      </c>
-      <c r="E21" t="n">
-        <v>7685</v>
-      </c>
-      <c r="F21" s="7" t="n">
-        <v>1073</v>
-      </c>
-      <c r="G21" t="n">
-        <v>3006</v>
-      </c>
-      <c r="H21" t="n">
-        <v>28</v>
-      </c>
-      <c r="I21" t="n">
-        <v>-155</v>
-      </c>
-      <c r="J21" t="n">
-        <v>357</v>
-      </c>
-      <c r="K21" t="n">
-        <v>2606</v>
-      </c>
-      <c r="L21" t="n">
-        <v>12250</v>
-      </c>
-      <c r="M21" t="n">
-        <v>-47580</v>
-      </c>
-      <c r="N21" t="n">
-        <v>18.39</v>
-      </c>
-      <c r="O21" t="inlineStr">
-        <is>
-          <t>中性</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>2345</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>智邦</t>
-        </is>
-      </c>
-      <c r="C22" t="n">
-        <v>1400</v>
-      </c>
-      <c r="D22" s="7" t="n">
-        <v>-3.45</v>
-      </c>
-      <c r="E22" t="n">
-        <v>5719</v>
-      </c>
-      <c r="F22" s="6" t="n">
-        <v>-565</v>
-      </c>
-      <c r="G22" t="n">
-        <v>159</v>
-      </c>
-      <c r="H22" t="n">
-        <v>-184</v>
-      </c>
-      <c r="I22" t="n">
-        <v>291</v>
-      </c>
-      <c r="J22" t="n">
-        <v>154</v>
-      </c>
-      <c r="K22" t="n">
-        <v>1931</v>
-      </c>
-      <c r="L22" t="n">
-        <v>9355</v>
-      </c>
-      <c r="M22" t="n">
-        <v>-140163</v>
-      </c>
-      <c r="N22" t="n">
-        <v>12.63</v>
-      </c>
-      <c r="O22" t="inlineStr">
-        <is>
-          <t>偏多</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>6640</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>均華</t>
-        </is>
-      </c>
-      <c r="C23" t="n">
-        <v>962</v>
-      </c>
-      <c r="D23" s="7" t="n">
-        <v>-0.1</v>
-      </c>
-      <c r="E23" t="n">
-        <v>826</v>
-      </c>
-      <c r="F23" s="7" t="n">
-        <v>78</v>
-      </c>
-      <c r="G23" t="n">
-        <v>85</v>
-      </c>
-      <c r="H23" t="n">
-        <v>-33</v>
-      </c>
-      <c r="I23" t="n">
-        <v>-118</v>
-      </c>
-      <c r="J23" t="n">
-        <v>-8</v>
-      </c>
-      <c r="K23" t="n">
-        <v>-2</v>
-      </c>
-      <c r="L23" t="n">
-        <v>-10</v>
-      </c>
-      <c r="M23" t="n">
-        <v>0</v>
-      </c>
-      <c r="N23" t="n">
-        <v>0</v>
-      </c>
-      <c r="O23" t="inlineStr">
-        <is>
-          <t>偏多</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>6187</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>萬潤</t>
-        </is>
-      </c>
-      <c r="C24" t="n">
-        <v>624</v>
-      </c>
-      <c r="D24" s="6" t="n">
-        <v>6.48</v>
-      </c>
-      <c r="E24" t="n">
-        <v>2040</v>
-      </c>
-      <c r="F24" s="7" t="n">
-        <v>2339</v>
-      </c>
-      <c r="G24" t="n">
-        <v>12425</v>
-      </c>
-      <c r="H24" t="n">
-        <v>0</v>
-      </c>
-      <c r="I24" t="n">
-        <v>0</v>
-      </c>
-      <c r="J24" t="n">
-        <v>18</v>
-      </c>
-      <c r="K24" t="n">
-        <v>464</v>
-      </c>
-      <c r="L24" t="n">
-        <v>-222</v>
-      </c>
-      <c r="M24" t="n">
-        <v>0</v>
-      </c>
-      <c r="N24" t="n">
-        <v>0</v>
-      </c>
-      <c r="O24" t="inlineStr">
-        <is>
-          <t>主力積極買進</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>2360</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>致茂</t>
-        </is>
-      </c>
-      <c r="C25" t="n">
-        <v>1380</v>
-      </c>
-      <c r="D25" s="6" t="n">
-        <v>9.960000000000001</v>
-      </c>
-      <c r="E25" t="n">
-        <v>2642</v>
-      </c>
-      <c r="F25" s="6" t="n">
-        <v>-1460</v>
-      </c>
-      <c r="G25" t="n">
-        <v>-2855</v>
-      </c>
-      <c r="H25" t="n">
-        <v>-782</v>
-      </c>
-      <c r="I25" t="n">
-        <v>96</v>
-      </c>
-      <c r="J25" t="n">
-        <v>4</v>
-      </c>
-      <c r="K25" t="n">
-        <v>1765</v>
-      </c>
-      <c r="L25" t="n">
-        <v>6387</v>
-      </c>
-      <c r="M25" t="n">
-        <v>-106273</v>
-      </c>
-      <c r="N25" t="n">
-        <v>23.26</v>
-      </c>
-      <c r="O25" t="inlineStr">
-        <is>
-          <t>偏空</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>3030</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>德律</t>
-        </is>
-      </c>
-      <c r="C26" t="n">
-        <v>223.5</v>
-      </c>
-      <c r="D26" s="6" t="n">
-        <v>9.83</v>
-      </c>
-      <c r="E26" t="n">
-        <v>10139</v>
-      </c>
-      <c r="F26" s="7" t="n">
-        <v>1915</v>
-      </c>
-      <c r="G26" t="n">
-        <v>3716</v>
-      </c>
-      <c r="H26" t="n">
-        <v>0</v>
-      </c>
-      <c r="I26" t="n">
-        <v>30</v>
-      </c>
-      <c r="J26" t="n">
-        <v>80</v>
-      </c>
-      <c r="K26" t="n">
-        <v>6977</v>
-      </c>
-      <c r="L26" t="n">
-        <v>30975</v>
-      </c>
-      <c r="M26" t="n">
-        <v>-58781</v>
-      </c>
-      <c r="N26" t="n">
-        <v>23.62</v>
-      </c>
-      <c r="O26" t="inlineStr">
-        <is>
-          <t>偏多</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>6515</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>穎崴</t>
-        </is>
-      </c>
-      <c r="C27" t="n">
-        <v>5115</v>
-      </c>
-      <c r="D27" s="6" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="E27" t="n">
-        <v>1016</v>
-      </c>
-      <c r="F27" s="6" t="n">
-        <v>-90</v>
-      </c>
-      <c r="G27" t="n">
-        <v>-71</v>
-      </c>
-      <c r="H27" t="n">
-        <v>74</v>
-      </c>
-      <c r="I27" t="n">
-        <v>-39</v>
-      </c>
-      <c r="J27" t="n">
-        <v>11</v>
-      </c>
-      <c r="K27" t="n">
-        <v>279</v>
-      </c>
-      <c r="L27" t="n">
-        <v>1696</v>
-      </c>
-      <c r="M27" t="n">
-        <v>-8884</v>
-      </c>
-      <c r="N27" t="n">
-        <v>6.74</v>
-      </c>
-      <c r="O27" t="inlineStr">
-        <is>
-          <t>主力積極賣出</t>
         </is>
       </c>
     </row>

--- a/outputs/monitor_xlsx/20260226.xlsx
+++ b/outputs/monitor_xlsx/20260226.xlsx
@@ -544,10 +544,6 @@
           <t>+0.00%</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -570,10 +566,6 @@
           <t>+1.11%</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -596,10 +588,6 @@
           <t>+0.32%</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -622,10 +610,6 @@
           <t>-0.69%</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -648,10 +632,6 @@
           <t>-0.57%</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -674,10 +654,6 @@
           <t>-0.34%</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -700,10 +676,6 @@
           <t>-3.19%</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -726,10 +698,6 @@
           <t>+3.90%</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -752,10 +720,6 @@
           <t>-0.32%</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -773,7 +737,6 @@
           <t>-105.64億</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
           <t>308.06億</t>
@@ -811,7 +774,6 @@
           <t>-10.58億</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
           <t>24.63億</t>
@@ -822,8 +784,6 @@
           <t>123.17億</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -841,15 +801,11 @@
           <t>141.14%</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
           <t>None%</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -867,11 +823,6 @@
           <t>-134.21億</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -889,15 +840,11 @@
           <t>7495口</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
           <t>11853口</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -915,7 +862,6 @@
           <t>-70.69億</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
           <t>-41.41億</t>
@@ -1020,10 +966,7 @@
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr"/>
-      <c r="B8" t="inlineStr"/>
-    </row>
+    <row r="8"/>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
@@ -1145,7 +1088,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V16"/>
+  <dimension ref="A1:V17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1179,6 +1122,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
@@ -1815,7 +1759,7 @@
         <v>-306</v>
       </c>
       <c r="I13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J13" t="n">
         <v>-22</v>
@@ -1998,6 +1942,45 @@
         <is>
           <t>N/A</t>
         </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>3167</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>大量</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>297</v>
+      </c>
+      <c r="D17" s="6" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="E17" t="n">
+        <v>1499</v>
+      </c>
+      <c r="G17" t="n">
+        <v>-103</v>
+      </c>
+      <c r="I17" t="n">
+        <v>357</v>
+      </c>
+      <c r="K17" t="n">
+        <v>6619</v>
+      </c>
+      <c r="L17" t="n">
+        <v>32318</v>
+      </c>
+      <c r="M17" t="n">
+        <v>-21431</v>
+      </c>
+      <c r="N17" t="n">
+        <v>4.27</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/monitor_xlsx/20260226.xlsx
+++ b/outputs/monitor_xlsx/20260226.xlsx
@@ -966,7 +966,6 @@
         </is>
       </c>
     </row>
-    <row r="8"/>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
@@ -1243,7 +1242,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0050</t>
+          <t>元大台灣50</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1251,20 +1250,23 @@
           <t>上市</t>
         </is>
       </c>
-      <c r="D4" t="n">
+      <c r="D4" s="6" t="n">
         <v>81.15000000000001</v>
       </c>
       <c r="E4" s="6" t="n">
         <v>0.06</v>
       </c>
-      <c r="F4" t="n">
+      <c r="F4" s="6" t="n">
         <v>133517</v>
       </c>
       <c r="G4" s="6" t="n">
         <v>-19326</v>
       </c>
       <c r="H4" t="n">
-        <v>-134274</v>
+        <v>-153600</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0</v>
       </c>
       <c r="J4" t="n">
         <v>30200</v>
@@ -1276,11 +1278,14 @@
         <v>8471</v>
       </c>
       <c r="M4" t="n">
-        <v>30912</v>
+        <v>39383</v>
       </c>
       <c r="N4" t="n">
         <v>-4112378</v>
       </c>
+      <c r="O4" t="n">
+        <v>9.02</v>
+      </c>
       <c r="V4" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1303,26 +1308,26 @@
           <t>上市</t>
         </is>
       </c>
-      <c r="D5" t="n">
+      <c r="D5" s="6" t="n">
         <v>1070</v>
       </c>
       <c r="E5" s="6" t="n">
         <v>1.9</v>
       </c>
-      <c r="F5" t="n">
+      <c r="F5" s="7" t="n">
         <v>10806</v>
       </c>
       <c r="G5" s="7" t="n">
         <v>1982</v>
       </c>
       <c r="H5" t="n">
-        <v>1888</v>
+        <v>3870</v>
       </c>
       <c r="I5" t="n">
         <v>-82</v>
       </c>
       <c r="J5" t="n">
-        <v>-815</v>
+        <v>-898</v>
       </c>
       <c r="K5" t="n">
         <v>376</v>
@@ -1331,11 +1336,14 @@
         <v>2840</v>
       </c>
       <c r="M5" t="n">
-        <v>11896</v>
+        <v>14736</v>
       </c>
       <c r="N5" t="n">
         <v>-78740</v>
       </c>
+      <c r="O5" t="n">
+        <v>7.75</v>
+      </c>
       <c r="V5" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1358,26 +1366,26 @@
           <t>上市</t>
         </is>
       </c>
-      <c r="D6" t="n">
+      <c r="D6" s="7" t="n">
         <v>1430</v>
       </c>
       <c r="E6" s="7" t="n">
         <v>-0.35</v>
       </c>
-      <c r="F6" t="n">
+      <c r="F6" s="6" t="n">
         <v>17965</v>
       </c>
       <c r="G6" s="6" t="n">
         <v>-2362</v>
       </c>
       <c r="H6" t="n">
-        <v>5813</v>
+        <v>3451</v>
       </c>
       <c r="I6" t="n">
         <v>987</v>
       </c>
       <c r="J6" t="n">
-        <v>2183</v>
+        <v>3170</v>
       </c>
       <c r="K6" t="n">
         <v>391</v>
@@ -1386,11 +1394,14 @@
         <v>6549</v>
       </c>
       <c r="M6" t="n">
-        <v>26276</v>
+        <v>32825</v>
       </c>
       <c r="N6" t="n">
         <v>-648840</v>
       </c>
+      <c r="O6" t="n">
+        <v>14.56</v>
+      </c>
       <c r="V6" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1413,26 +1424,26 @@
           <t>上市</t>
         </is>
       </c>
-      <c r="D7" t="n">
+      <c r="D7" s="7" t="n">
         <v>1995</v>
       </c>
       <c r="E7" s="7" t="n">
         <v>-0.99</v>
       </c>
-      <c r="F7" t="n">
+      <c r="F7" s="6" t="n">
         <v>74411</v>
       </c>
       <c r="G7" s="6" t="n">
         <v>-18137</v>
       </c>
       <c r="H7" t="n">
-        <v>-19805</v>
+        <v>-37942</v>
       </c>
       <c r="I7" t="n">
         <v>1202</v>
       </c>
       <c r="J7" t="n">
-        <v>7692</v>
+        <v>8894</v>
       </c>
       <c r="K7" t="n">
         <v>520</v>
@@ -1441,11 +1452,14 @@
         <v>22312</v>
       </c>
       <c r="M7" t="n">
-        <v>85837</v>
+        <v>108149</v>
       </c>
       <c r="N7" t="n">
         <v>-6482906</v>
       </c>
+      <c r="O7" t="n">
+        <v>9.06</v>
+      </c>
       <c r="V7" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1468,26 +1482,26 @@
           <t>上市</t>
         </is>
       </c>
-      <c r="D8" t="n">
+      <c r="D8" s="7" t="n">
         <v>1400</v>
       </c>
       <c r="E8" s="7" t="n">
         <v>-3.45</v>
       </c>
-      <c r="F8" t="n">
+      <c r="F8" s="6" t="n">
         <v>5719</v>
       </c>
       <c r="G8" s="6" t="n">
         <v>-565</v>
       </c>
       <c r="H8" t="n">
-        <v>724</v>
+        <v>159</v>
       </c>
       <c r="I8" t="n">
         <v>-184</v>
       </c>
       <c r="J8" t="n">
-        <v>474</v>
+        <v>291</v>
       </c>
       <c r="K8" t="n">
         <v>154</v>
@@ -1496,11 +1510,14 @@
         <v>1931</v>
       </c>
       <c r="M8" t="n">
-        <v>7424</v>
+        <v>9355</v>
       </c>
       <c r="N8" t="n">
         <v>-140163</v>
       </c>
+      <c r="O8" t="n">
+        <v>12.63</v>
+      </c>
       <c r="V8" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1523,26 +1540,26 @@
           <t>上市</t>
         </is>
       </c>
-      <c r="D9" t="n">
+      <c r="D9" s="6" t="n">
         <v>1380</v>
       </c>
       <c r="E9" s="6" t="n">
         <v>9.960000000000001</v>
       </c>
-      <c r="F9" t="n">
+      <c r="F9" s="6" t="n">
         <v>2642</v>
       </c>
       <c r="G9" s="6" t="n">
         <v>-1460</v>
       </c>
       <c r="H9" t="n">
-        <v>-1394</v>
+        <v>-2855</v>
       </c>
       <c r="I9" t="n">
         <v>-782</v>
       </c>
       <c r="J9" t="n">
-        <v>878</v>
+        <v>96</v>
       </c>
       <c r="K9" t="n">
         <v>4</v>
@@ -1551,11 +1568,14 @@
         <v>1765</v>
       </c>
       <c r="M9" t="n">
-        <v>4622</v>
+        <v>6387</v>
       </c>
       <c r="N9" t="n">
         <v>-106273</v>
       </c>
+      <c r="O9" t="n">
+        <v>30.02</v>
+      </c>
       <c r="V9" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1578,26 +1598,26 @@
           <t>上市</t>
         </is>
       </c>
-      <c r="D10" t="n">
+      <c r="D10" s="6" t="n">
         <v>2440</v>
       </c>
       <c r="E10" s="6" t="n">
         <v>0.83</v>
       </c>
-      <c r="F10" t="n">
+      <c r="F10" s="6" t="n">
         <v>4713</v>
       </c>
       <c r="G10" s="6" t="n">
         <v>-45</v>
       </c>
       <c r="H10" t="n">
-        <v>-1610</v>
+        <v>-1656</v>
       </c>
       <c r="I10" t="n">
         <v>-46</v>
       </c>
       <c r="J10" t="n">
-        <v>1487</v>
+        <v>1440</v>
       </c>
       <c r="K10" t="n">
         <v>83</v>
@@ -1606,11 +1626,14 @@
         <v>2177</v>
       </c>
       <c r="M10" t="n">
-        <v>8753</v>
+        <v>10930</v>
       </c>
       <c r="N10" t="n">
         <v>-89468</v>
       </c>
+      <c r="O10" t="n">
+        <v>24.19</v>
+      </c>
       <c r="V10" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1633,26 +1656,26 @@
           <t>上市</t>
         </is>
       </c>
-      <c r="D11" t="n">
+      <c r="D11" s="6" t="n">
         <v>2145</v>
       </c>
       <c r="E11" s="6" t="n">
         <v>3.12</v>
       </c>
-      <c r="F11" t="n">
+      <c r="F11" s="7" t="n">
         <v>1361</v>
       </c>
       <c r="G11" s="7" t="n">
         <v>66</v>
       </c>
       <c r="H11" t="n">
-        <v>134</v>
+        <v>200</v>
       </c>
       <c r="I11" t="n">
         <v>-10</v>
       </c>
       <c r="J11" t="n">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="K11" t="n">
         <v>28</v>
@@ -1661,11 +1684,14 @@
         <v>4245</v>
       </c>
       <c r="M11" t="n">
-        <v>16753</v>
+        <v>20998</v>
       </c>
       <c r="N11" t="n">
         <v>-19134</v>
       </c>
+      <c r="O11" t="n">
+        <v>23.86</v>
+      </c>
       <c r="V11" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1688,26 +1714,26 @@
           <t>上市</t>
         </is>
       </c>
-      <c r="D12" t="n">
+      <c r="D12" s="6" t="n">
         <v>5115</v>
       </c>
       <c r="E12" s="6" t="n">
         <v>2.3</v>
       </c>
-      <c r="F12" t="n">
+      <c r="F12" s="6" t="n">
         <v>1016</v>
       </c>
       <c r="G12" s="6" t="n">
         <v>-90</v>
       </c>
       <c r="H12" t="n">
-        <v>19</v>
+        <v>-71</v>
       </c>
       <c r="I12" t="n">
         <v>74</v>
       </c>
       <c r="J12" t="n">
-        <v>-113</v>
+        <v>-39</v>
       </c>
       <c r="K12" t="n">
         <v>11</v>
@@ -1716,11 +1742,14 @@
         <v>279</v>
       </c>
       <c r="M12" t="n">
-        <v>1417</v>
+        <v>1696</v>
       </c>
       <c r="N12" t="n">
         <v>-8884</v>
       </c>
+      <c r="O12" t="n">
+        <v>16.45</v>
+      </c>
       <c r="V12" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1743,23 +1772,23 @@
           <t>上櫃</t>
         </is>
       </c>
-      <c r="D13" t="n">
-        <v>2315</v>
+      <c r="D13" s="6" t="n">
+        <v>2365</v>
       </c>
       <c r="E13" s="6" t="n">
-        <v>9.98</v>
-      </c>
-      <c r="F13" t="n">
-        <v>2730</v>
+        <v>2.16</v>
+      </c>
+      <c r="F13" s="6" t="n">
+        <v>2182</v>
       </c>
       <c r="G13" s="6" t="n">
         <v>-160</v>
       </c>
       <c r="H13" t="n">
-        <v>-306</v>
+        <v>-466</v>
       </c>
       <c r="I13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="J13" t="n">
         <v>-22</v>
@@ -1771,11 +1800,14 @@
         <v>10</v>
       </c>
       <c r="M13" t="n">
-        <v>-233</v>
+        <v>-223</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
       </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
       <c r="V13" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1798,26 +1830,26 @@
           <t>上櫃</t>
         </is>
       </c>
-      <c r="D14" t="n">
-        <v>449.5</v>
+      <c r="D14" s="6" t="n">
+        <v>586</v>
       </c>
       <c r="E14" s="6" t="n">
-        <v>4.78</v>
-      </c>
-      <c r="F14" t="n">
-        <v>3871</v>
+        <v>9.94</v>
+      </c>
+      <c r="F14" s="6" t="n">
+        <v>32773</v>
       </c>
       <c r="G14" s="6" t="n">
         <v>-2009</v>
       </c>
       <c r="H14" t="n">
-        <v>3764</v>
+        <v>1755</v>
       </c>
       <c r="I14" t="n">
         <v>312</v>
       </c>
       <c r="J14" t="n">
-        <v>2486</v>
+        <v>2798</v>
       </c>
       <c r="K14" t="n">
         <v>28</v>
@@ -1826,11 +1858,14 @@
         <v>515</v>
       </c>
       <c r="M14" t="n">
-        <v>-2042</v>
+        <v>-1527</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
       </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
       <c r="V14" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1853,20 +1888,23 @@
           <t>上櫃</t>
         </is>
       </c>
-      <c r="D15" t="n">
-        <v>974</v>
-      </c>
-      <c r="E15" s="6" t="n">
-        <v>9.93</v>
-      </c>
-      <c r="F15" t="n">
-        <v>1350</v>
+      <c r="D15" s="7" t="n">
+        <v>1105</v>
+      </c>
+      <c r="E15" s="7" t="n">
+        <v>-2.64</v>
+      </c>
+      <c r="F15" s="7" t="n">
+        <v>6341</v>
       </c>
       <c r="G15" s="7" t="n">
         <v>2339</v>
       </c>
       <c r="H15" t="n">
-        <v>10086</v>
+        <v>12425</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1878,11 +1916,14 @@
         <v>464</v>
       </c>
       <c r="M15" t="n">
-        <v>-686</v>
+        <v>-222</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
       </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
       <c r="V15" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1905,26 +1946,26 @@
           <t>上櫃</t>
         </is>
       </c>
-      <c r="D16" t="n">
-        <v>1600</v>
-      </c>
-      <c r="E16" s="6" t="n">
-        <v>4.92</v>
-      </c>
-      <c r="F16" t="n">
-        <v>904</v>
+      <c r="D16" s="7" t="n">
+        <v>1625</v>
+      </c>
+      <c r="E16" s="7" t="n">
+        <v>-6.07</v>
+      </c>
+      <c r="F16" s="7" t="n">
+        <v>1168</v>
       </c>
       <c r="G16" s="7" t="n">
         <v>78</v>
       </c>
       <c r="H16" t="n">
-        <v>7</v>
+        <v>85</v>
       </c>
       <c r="I16" t="n">
         <v>-33</v>
       </c>
       <c r="J16" t="n">
-        <v>-85</v>
+        <v>-118</v>
       </c>
       <c r="K16" t="n">
         <v>-8</v>
@@ -1933,11 +1974,14 @@
         <v>-2</v>
       </c>
       <c r="M16" t="n">
-        <v>-8</v>
+        <v>-10</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
       </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
       <c r="V16" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1955,32 +1999,46 @@
           <t>大量</t>
         </is>
       </c>
-      <c r="C17" t="n">
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="D17" s="6" t="n">
         <v>297</v>
       </c>
-      <c r="D17" s="6" t="n">
+      <c r="E17" s="6" t="n">
         <v>0.68</v>
       </c>
-      <c r="E17" t="n">
+      <c r="F17" s="7" t="n">
         <v>1499</v>
       </c>
-      <c r="G17" t="n">
-        <v>-103</v>
+      <c r="G17" s="7" t="n">
+        <v>92</v>
+      </c>
+      <c r="H17" t="n">
+        <v>-11</v>
       </c>
       <c r="I17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" t="n">
         <v>357</v>
       </c>
       <c r="K17" t="n">
+        <v>11</v>
+      </c>
+      <c r="L17" t="n">
         <v>6619</v>
       </c>
-      <c r="L17" t="n">
+      <c r="M17" t="n">
         <v>32318</v>
       </c>
-      <c r="M17" t="n">
+      <c r="N17" t="n">
         <v>-21431</v>
       </c>
-      <c r="N17" t="n">
-        <v>4.27</v>
+      <c r="O17" t="n">
+        <v>22.94</v>
       </c>
     </row>
   </sheetData>
